--- a/sources/kuma_step9.xlsx
+++ b/sources/kuma_step9.xlsx
@@ -929,6 +929,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
@@ -991,6 +996,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
@@ -1053,6 +1063,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
@@ -1113,6 +1128,11 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>d84f5821-e8c2-4b13-80d7-7f78bb38c6d1</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">

--- a/sources/kuma_step9.xlsx
+++ b/sources/kuma_step9.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AD105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="49" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="93" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="93" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,57 +622,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Bear Bite</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bear Bite</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>8ffa663f-90d1-4c2a-806e-9edd0fcb53a9</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>e4d33ebc-baa9-4a9a-a9e7-b42e09c1ce65</t>
         </is>
@@ -683,57 +689,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Bear Hug</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Bear Hug</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>6d069606-1ead-41f6-a086-5f3632c99bc5</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>3d1a42ce-4e2c-4198-8302-315ee07e19e5</t>
         </is>
@@ -750,62 +756,62 @@
           <t>f,f+1+4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Stone Head</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Throw can be tech rolled, damage remains the same.</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>7868e887-48e7-4967-ae5c-b38532530918</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>ee261a0f-70d3-447e-a11d-d8db8323e986</t>
         </is>
@@ -822,62 +828,62 @@
           <t>hcb,f+1+2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Circus Roll</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Circus Roll</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>f6abfa42-5126-4d5d-810a-37f2ddd291f1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>e978f020-4aec-451f-9000-58cfbc7f551b</t>
         </is>
@@ -894,52 +900,52 @@
           <t>3+4 ,f+1+2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Mauling Bear</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Mauling Bear</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -963,50 +969,55 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Choke Slam</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Choke Slam</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>10,15,25</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>10,15,25</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1030,50 +1041,55 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Rag Doll</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Rag Doll</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1097,50 +1113,55 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Bear Swing</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Bear Swing</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>d84f5821-e8c2-4b13-80d7-7f78bb38c6d1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>d84f5821-e8c2-4b13-80d7-7f78bb38c6d1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1177,125 +1198,130 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="S13" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
+      <c r="T13" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T13" s="1" t="inlineStr">
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
+      <c r="W13" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X13" s="1" t="inlineStr">
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AC13" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC13" s="1" t="inlineStr">
+      <c r="AD13" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1312,77 +1338,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>2d88f06c-8087-438f-a007-037163c79e0e</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>4b7052e8-ed9f-45ac-ac8e-faa36828dc33</t>
         </is>
@@ -1399,77 +1425,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>f8a27033-fa93-4bbc-858f-ec515a028df7</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>5606bad0-869c-45f1-8da6-13b48b344b77</t>
         </is>
@@ -1486,77 +1512,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>8b80f948-b6f4-48c2-b30d-514d433939e8</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>5362d924-a650-44a9-94af-7d2ddac4d789</t>
         </is>
@@ -1573,77 +1599,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>4a1d670b-89f6-4b35-8f6f-e4dfeb955e68</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>efa9c2a4-b8bb-4282-9c49-288f38513475</t>
         </is>
@@ -1660,77 +1686,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>930dc75f-67fc-4757-8f33-8135b03b44e3</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>6d23d07c-d6a4-4504-b22b-02e1878b5091</t>
         </is>
@@ -1747,77 +1773,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>5483c1ca-f1c5-44d8-a864-f6e454f80934</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>71699a51-3a3a-4465-a9a1-274468419511</t>
         </is>
@@ -1834,77 +1860,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>7e9935ed-6cce-487c-9fbe-99628529bf8f</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>c3ea7046-92a2-47d2-98b7-8fd3ed47fb7c</t>
         </is>
@@ -1921,77 +1947,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>6e420769-fc91-4c8c-89cc-0eb729eb446e</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>f3072438-4acc-4fd5-af67-63da81945c9b</t>
         </is>
@@ -2008,77 +2034,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>57b400b9-485a-475e-881d-bd8edcb66e66</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>42aa6324-6699-401f-bfc2-df296858a6c0</t>
         </is>
@@ -2095,77 +2121,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>48d390f2-8426-4430-b64f-6f7fd325724f</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>08f47bac-44d8-4dc0-88b9-2a48ef9dbbb2</t>
         </is>
@@ -2182,77 +2208,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>6efb1770-0dc6-4cfb-9559-e92b2fb12cf0</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>f8e7855c-ad4d-4497-8f86-35820af7c8b5</t>
         </is>
@@ -2269,77 +2295,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>25c30d7d-6910-471d-ace9-0f1b9643e7d6</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>11b9be52-b2ba-464b-9b8c-072ab30216cf</t>
         </is>
@@ -2356,77 +2382,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>f0997a35-6b5e-4a68-b468-fbc1db2742d0</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>ad5c9820-5bd4-4925-a0af-ca4ef4d34f24</t>
         </is>
@@ -2443,77 +2469,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>1ae84d7f-e549-49ff-ba5e-da6d786a8bcf</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>a502ec3d-a0a7-4981-bd54-c5fa0b51be16</t>
         </is>
@@ -2530,77 +2556,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>e7792c99-49a4-46a0-b867-12d49829edf0</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>f47434cc-6dbd-4208-90c5-5c0a80165742</t>
         </is>
@@ -2617,77 +2643,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>18897a2c-54b7-48f8-b629-f7afb23ba461</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>470adc11-43df-4616-836b-7bd1b4f4c4b6</t>
         </is>
@@ -2704,77 +2730,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>67379736-126b-4983-bf6b-a98410de197f</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>b5f35d76-2f54-4790-98a2-03660a3663fb</t>
         </is>
@@ -2791,77 +2817,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+25</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>3bbb3ec7-40b0-4f21-a3f1-bfbd1a7d5f03</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>7752727d-598b-44a2-ac6d-828d99ef6d09</t>
         </is>
@@ -2878,77 +2904,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>111b159b-e303-4dc3-aab9-f9bdac7e2235</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>e8a0de98-a910-47b9-ba10-748bc228edfb</t>
         </is>
@@ -2965,77 +2991,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>129f0a19-73c2-405d-b61b-3408e9a13f61</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>cc600486-96df-4367-9aaa-4cd2546d8651</t>
         </is>
@@ -3052,77 +3078,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>936673cd-500d-414e-852b-9db3a81c60fc</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>5ce04d7e-0a1d-46ee-9d01-bc9a7d4a5a08</t>
         </is>
@@ -3139,77 +3165,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>10753224-ec13-42ed-b3a7-7890ef45e92d</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>d47afabb-305a-4af6-beda-a875079411fe</t>
         </is>
@@ -3226,77 +3252,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>5db2aed3-4c50-4c69-b653-92728b93dcee</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>a771c59f-c989-4ea0-9aef-0d54faa12606</t>
         </is>
@@ -3313,77 +3339,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>f837108a-8ccd-4fbe-876f-6bae4976802e</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>116098b6-dbde-4457-872a-c16805c61717</t>
         </is>
@@ -3420,125 +3446,130 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="I40" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="K40" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K40" s="1" t="inlineStr">
+      <c r="L40" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="M40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr">
+      <c r="N40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="O40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
+      <c r="P40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="Q40" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr">
+      <c r="S40" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S40" s="1" t="inlineStr">
+      <c r="T40" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T40" s="1" t="inlineStr">
+      <c r="U40" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
+      <c r="V40" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
+      <c r="W40" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
+      <c r="X40" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X40" s="1" t="inlineStr">
+      <c r="Y40" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB40" s="1" t="inlineStr">
+      <c r="AC40" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC40" s="1" t="inlineStr">
+      <c r="AD40" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3555,87 +3586,87 @@
           <t>1 ,1 ,1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Bear Hammer</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Bear Hammer</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>18,15,18</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>18,15,18</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>8cd27751-4bdf-4c8d-817c-ce65e1291aca</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>b68866fe-2244-45de-94ca-939e4721a998</t>
         </is>
@@ -3652,97 +3683,97 @@
           <t>f+1 ,1 ,1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Bear Heaven Cannon</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Bear Heaven Cannon</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>+1 -15 -14</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>+1 -15 -14</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>+12 -3 KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+12 -3 KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>+12 -4 KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>+12 -4 KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>10,8,14</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>10,8,14</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>eaba9c6c-a758-41a3-a13d-23dcad22150a</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>8f5c2acf-fa8b-4021-b502-b9f0bec132a0</t>
         </is>
@@ -3759,97 +3790,97 @@
           <t>DF+1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Bear Upper Rush</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Bear Upper Rush</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-11 -13 -1 -9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-11 -13 -1 -9</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>0 +2 +10 +3</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>0 +2 +10 +3</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>0 +2 +10 +3</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>0 +2 +10 +3</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>10,15,10,15</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>10,15,10,15</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Juggles on last the last hit if the 1st hit is a CH.</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>c885932a-1611-4eef-af83-be03cf887f52</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>a59e2a97-9ac7-4d59-887b-bcb71b7b87b5</t>
         </is>
@@ -3858,12 +3889,12 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,1</t>
+          <t>DF,1 ,2 ,1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3873,95 +3904,100 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>FC+DF+1,2,1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-6 -8 -2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-6 -8 -2</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Juggles on last the last hit if the 1st hit is a CH.</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>ae25a351-a7ed-461e-92cf-3da8cfe5699d</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>499c922a-d1b8-40d5-99e6-87af142efc96</t>
         </is>
@@ -3978,87 +4014,87 @@
           <t>WS+1 ,2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Grizzly Upper - Grizzly Claw</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Grizzly Upper - Grizzly Claw</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-15 -17</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-15 -17</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>12,27</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>12,27</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>fb6e5043-c989-4f36-be85-4237cc95538e</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>b2a4fbb2-d462-4093-a64b-19219ec28211</t>
         </is>
@@ -4075,92 +4111,92 @@
           <t>FC+df+1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Grizzly Windmill</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Grizzly Windmill</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-22 -22 -2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-22 -22 -2</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>12,15,15</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>12,15,15</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>ad535306-234d-4132-8e43-490a65e15c14</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>3a271293-7f43-4651-97e1-0fc339896aad</t>
         </is>
@@ -4177,92 +4213,92 @@
           <t>FC+df+1 ,2 ,1 ,1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Windmill Backhand</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Grizzly Windmill – Windmill Backhand</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-22 -22 -2 +20</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>-12 -12 -12 KD</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>-12 -12 -12 KD</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>12,15,15,30</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>mmmh</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>CF GB</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>ba8813bc-c9d8-421f-9313-d91aadbe9c1c</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>31100332-9043-4ad1-ae7a-47606f8c4cef</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>ad535306-234d-4132-8e43-490a65e15c14</t>
         </is>
@@ -4279,92 +4315,92 @@
           <t>FC+1 ,1 ,1 ,2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Bear Rush</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Bear Rush</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-8 +2 -2 +3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-8 +2 -2 +3</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>12,8,12,12</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>12,8,12,12</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>9b2b97bc-6e77-4c1b-88b2-34dc9ededa50</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>716338ea-a810-4179-bd10-b72c74ef6acb</t>
         </is>
@@ -4381,92 +4417,92 @@
           <t>FC+1 ,1 ,1 ,2 ,d+1</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Bear Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-8 +2 -2 +3 -17</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3 -7</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3 -7</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>12,8,12,12,8</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>LLmmL</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>b9ab4080-fe96-47c7-9885-ed6a81dcf104</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>d11f2fcf-e8ad-48b9-b439-35879faefb5f</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>9b2b97bc-6e77-4c1b-88b2-34dc9ededa50</t>
         </is>
@@ -4483,92 +4519,92 @@
           <t>FC+1 ,1 ,1 ,2 ,df+1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Bear Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-8 +2 -2 +3 -1</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3 +10</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3 +10</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>12,8,12,12,15</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>LLmmm</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>81b2cddf-e752-4290-8339-6a82a3f8b286</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>2133ac25-2cdd-47d2-8e39-04b30065c044</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>9b2b97bc-6e77-4c1b-88b2-34dc9ededa50</t>
         </is>
@@ -4585,87 +4621,87 @@
           <t>FC+1 ,1 ,1 ,2 ,f+1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Bear Rush – High Punch</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-8 +2 -2 +3 -17</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3 -5</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>+2 +12 -2 +3 -5</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>12,8,12,12,12</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>LLmmh</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>44eb6085-b94c-402d-9602-0ae175249973</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>2bc073f6-c6fe-48a9-b3eb-feef8a50027d</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>9b2b97bc-6e77-4c1b-88b2-34dc9ededa50</t>
         </is>
@@ -4674,12 +4710,12 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Df+1 ,2</t>
+          <t>DF,1 ,2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4689,90 +4725,95 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>FC+DF+1,2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-6 -8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-6 -8</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>+5 +3</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>+5 +3</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>+5 +3</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>+5 +3</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>75de4596-1735-4639-ac00-6a07c0c533e5</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>1987f2a5-d5bc-4d3a-a086-c1b102206dc7</t>
         </is>
@@ -4786,95 +4827,95 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,d+1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+          <t>DF,1 ,2 ,d+1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-6 -8 -17</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>+5 +3 -7</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>+5 +3 -7</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>15,12,8</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>mmL</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>0a8ac3e3-bb71-412f-979c-81946c200e43</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>11496d20-cf33-4430-8f06-9f78d7519db4</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>75de4596-1735-4639-ac00-6a07c0c533e5</t>
         </is>
@@ -4888,95 +4929,95 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,df+1</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+          <t>DF,1 ,2 ,df+1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-6 -8 -1</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+5 +3 +10</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>+5 +3 +10</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>40ed627d-08e7-4828-9c3c-1efd9aa24e42</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>82e81aa3-e47e-4627-9893-fd11bd17313e</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>75de4596-1735-4639-ac00-6a07c0c533e5</t>
         </is>
@@ -4990,90 +5031,90 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,f+1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+          <t>DF,1 ,2 ,f+1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-6 -8 -17</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+5 +3 -5</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>+5 +3 -5</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>15,12,12</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>e5f142aa-98ea-49a6-bbf9-0805ba34a694</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>bfbba39d-cd6c-4410-a868-848a1b5e56e8</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>75de4596-1735-4639-ac00-6a07c0c533e5</t>
         </is>
@@ -5090,87 +5131,87 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Bear Knuckle</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Bear Knuckle</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>54fb02f5-5fbd-4f7d-8b4d-a971cec2c321</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>1ef988f5-d193-4f00-ae28-c60afc1aad9d</t>
         </is>
@@ -5187,92 +5228,92 @@
           <t>1+2~f</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>– Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Bear Knuckle – Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-15 x</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD x</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>KD x</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>21,-</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>90ce6d1b-b4d9-426f-b5bd-f450545cf52c</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>891d4b7f-adf1-4f38-b2d9-f8fc0a3718c0</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>54fb02f5-5fbd-4f7d-8b4d-a971cec2c321</t>
         </is>
@@ -5289,92 +5330,92 @@
           <t>1+2 &lt;1+2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>– Claw Uppercut</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Bear Knuckle – Claw Uppercut</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-15 -22</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>0dd241a2-d488-4c9e-8620-67df7a841bae</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>709f1ea8-92e7-4df3-ab8e-3e7015dbc451</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>54fb02f5-5fbd-4f7d-8b4d-a971cec2c321</t>
         </is>
@@ -5391,92 +5432,92 @@
           <t>WS+1+2 &lt;1+2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Claw Upper - Bear Knuckle</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Claw Upper - Bear Knuckle</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-16 -15</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-16 -15</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>ec9e6949-72f2-43bf-8aa8-39e4e8e55196</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>25fc1d7d-677e-405d-b5c9-2e69bba2ec52</t>
         </is>
@@ -5493,92 +5534,92 @@
           <t>WS+1+2 &lt;1+2~f</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>– Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Claw Upper - Bear Knuckle – Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-16 -15 x</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD KD x</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>KD KD x</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>21,17,-</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>mm-</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>aae54c5e-7bbc-424e-b99b-d14db40ec2c1</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>aef27e03-56c2-425b-a845-f21a3ead3aa7</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>ec9e6949-72f2-43bf-8aa8-39e4e8e55196</t>
         </is>
@@ -5595,92 +5636,92 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Grizzly Scissors</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Grizzly Scissors</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>16970712-b15a-4a48-99d9-646567fc94b1</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>8fee3a47-998f-4141-8b45-4d903e76de11</t>
         </is>
@@ -5697,92 +5738,92 @@
           <t>uf+1+2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Big Bear Belly Flop</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Big Bear Belly Flop</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>895f6dec-0228-4ebd-b88d-8e2b2ee2ebf6</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>a5269e4a-8f25-465c-9b67-1cb924d6b8a8</t>
         </is>
@@ -5799,92 +5840,92 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Demon Bear</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Demon Bear</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>This moves only works with Heihachi Mishima on your team.</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>30f809ec-a21c-40a7-95e5-1bacf0192294</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>baa8efb5-32e2-4d8b-b7c9-e15b6decdff3</t>
         </is>
@@ -5901,92 +5942,92 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Grizzly Head Butt</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Grizzly Head Butt</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>KS GB</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>26d76e7d-5dfd-4e60-84bd-7b76ac92ee5d</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>56020b51-4159-4599-b415-9db96d64f776</t>
         </is>
@@ -6003,97 +6044,97 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Demon Bear Fist</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Demon Bear Fist</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>35629b78-cf57-4fa8-8d31-2b94233ca690</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>e292e168-866d-4950-8508-e81b0eb5b8fd</t>
         </is>
@@ -6110,97 +6151,97 @@
           <t>2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Punch - Elbow - Upper</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Punch - Elbow - Upper</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>0 0 -15</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>0 0 -15</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-7 +2 KD</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>-7 +2 KD</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>-7 +2 KD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>-7 +2 KD</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>12,15,20</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>12,15,20</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>f6ca1570-1faf-4d56-85e7-6e68a202bb7b</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>8534f402-b6d8-4ac2-8d4c-1df0df7e16da</t>
         </is>
@@ -6217,92 +6258,92 @@
           <t>DF+2 ,1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Bear Upper Rush</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Bear Upper Rush</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-11 -6 -9 -1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-11 -6 -9 -1</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>10,15,12,15</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>10,15,12,15</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>7c86dcba-17b0-47ef-a6c7-05cf5e0aeb19</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>d1229476-1ab1-4f74-919f-236115c79638</t>
         </is>
@@ -6311,12 +6352,12 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6326,90 +6367,95 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>FC+df+2</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Short Hammer Rush</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Short Hammer Rush</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>a70a4eab-7017-4367-9410-b81eca9f900b</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>4c1fe6b4-5920-4fb3-bbba-c325769be19c</t>
         </is>
@@ -6423,95 +6469,95 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Df+2 ,d+1</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+          <t>DF,2 ,d+1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-13 -17</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>-2 -7</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>-2 -7</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>10,8</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>69876114-5ad9-492c-bbf4-2aabf6694406</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>1e2b2f40-ea21-43f3-8e96-1b546524599e</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>a70a4eab-7017-4367-9410-b81eca9f900b</t>
         </is>
@@ -6525,95 +6571,95 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Df+2 ,df+1</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+          <t>DF,2 ,df+1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Short Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-13 -1</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>-2 +10</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>-2 +10</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>20994bb7-71ff-4fe2-a6a5-ce8c1b836fdf</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>567810e7-fc6f-41ef-8112-f6da63e1dfe1</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>a70a4eab-7017-4367-9410-b81eca9f900b</t>
         </is>
@@ -6627,90 +6673,90 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Df+2 ,f+1</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+          <t>DF,2 ,f+1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Short Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-13 -17</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>-2 -5</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>-2 -5</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>10,12</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>fc82496c-c503-46e3-bac3-92f0ce7b2592</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>267444e4-c34b-4443-8478-9e05b0a91ff8</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>a70a4eab-7017-4367-9410-b81eca9f900b</t>
         </is>
@@ -6719,12 +6765,12 @@
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Df+2 ,1 ,2</t>
+          <t>DF,2 ,1 ,2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6734,95 +6780,100 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>FC+DF+2,1,2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Quick Uppercut Rush</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Quick Uppercut Rush</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-13 -1 -9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-13 -1 -9</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>15,10,15</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>15,10,15</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>JG  RC</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>Juggles on last the last hit if the 1st hit is a CH.</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>532736f0-ec3b-4f46-8a57-6fc7cd5bc191</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>835b5fd1-7fe3-4dce-b751-5f05f50f60ab</t>
         </is>
@@ -6839,92 +6890,92 @@
           <t>b,db,d,DF+2</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Grizzly Claw</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Grizzly Claw</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>46ae02e5-d8ef-46a8-9ae7-28a01129dbf9</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>4b192795-b89d-4014-a17d-3b690e82ce80</t>
         </is>
@@ -6941,87 +6992,87 @@
           <t>b,f+2+3</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Salmon Hunter</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Salmon Hunter</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>b338a8e9-2eae-4f0b-b326-bb6097714cad</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>e4e339d3-d9f4-48d2-b854-5191e06fc25b</t>
         </is>
@@ -7038,92 +7089,92 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Pancake Press</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Pancake Press</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>If the Pancake Press misses the opponent, Panda or Kuma can chain into Sit Down extentions.</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>85749ef9-499a-4152-9094-6578e05f4cce</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>6312a228-1f60-4667-887c-4397b799f0a0</t>
         </is>
@@ -7140,47 +7191,47 @@
           <t>d+3+4</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>335e7696-dcf0-421e-b7d5-f7915bec6059</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>3a746cfb-2e10-4e81-845e-da2d4c4492bb</t>
         </is>
@@ -7197,52 +7248,52 @@
           <t>d+3+4,B</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Sit Down – Roll Back</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>e94aca3a-d9dd-44da-bf46-53fca9daff4f</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>d153c37a-f5ec-4c34-8697-8dc00b682eb1</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>335e7696-dcf0-421e-b7d5-f7915bec6059</t>
         </is>
@@ -7259,52 +7310,52 @@
           <t>d+3+4,F</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Sit Down – Roll Forward</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>cb3a62e3-7f1a-439a-b186-7b41dd307f25</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>29356cbd-ffd5-432c-b0ac-81f5f6eef0d8</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>335e7696-dcf0-421e-b7d5-f7915bec6059</t>
         </is>
@@ -7321,150 +7372,170 @@
           <t>d+3+4 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>d+3+4,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>– Sitting Claws</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Sit Down – Sitting Claws</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>-,10,10,10,10</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>-llll</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>6f5a5ac7-4e00-4362-9c8d-2f5883004b79</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>3a2519d3-2d39-4b4c-99a1-641a51b23b5a</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>335e7696-dcf0-421e-b7d5-f7915bec6059</t>
         </is>
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+          <t>d+1+2</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Spring Claw - Sit Down</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Spring Claw - Sit Down</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>9d92e1b7-2094-41cf-a815-aa5d2aa2f0d5</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>eac81ff6-75c1-4392-8b1f-3a1a6f09cef1</t>
         </is>
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
@@ -7472,90 +7543,100 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KND d+1+2 ,1 ,2 ,1 ,2</t>
+          <t>d+1+2 ,1 ,2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>KND d+1+2,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>– Sitting Claws</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Spring Claw - Sit Down – Sitting Claws</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>12,10,10,10,10</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>mllll</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>3588b778-27db-4657-a3f7-c308b677ec91</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>daf628f5-72bf-4511-a55d-a38e8e616987</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>9d92e1b7-2094-41cf-a815-aa5d2aa2f0d5</t>
         </is>
@@ -7572,52 +7653,52 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>eccb45f0-ca41-420b-98df-1b2137270030</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>c8db8eb8-7476-4a8b-b9fc-ac3242108986</t>
         </is>
@@ -7634,47 +7715,47 @@
           <t>1+3+4</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Dancing Taunt</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Dancing Taunt</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>a2abff01-211a-4a66-97a1-88a18c9251c4</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>34777817-1aa5-4233-998d-7bc5841807cc</t>
         </is>
@@ -7691,82 +7772,82 @@
           <t>D+4</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Turn Around Dance</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Turn Around Dance</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>20,60</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>20,60</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>When opponent is on the ground only.</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>0c30cac1-9313-4c1a-a4ff-f9cc0ff92e8b</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>16a9aed5-5e87-445c-a089-d0e3d776f2ec</t>
         </is>
@@ -7803,125 +7884,130 @@
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
+      <c r="H87" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H87" s="1" t="inlineStr">
+      <c r="I87" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I87" s="1" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J87" s="1" t="inlineStr">
+      <c r="K87" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K87" s="1" t="inlineStr">
+      <c r="L87" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L87" s="1" t="inlineStr">
+      <c r="M87" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M87" s="1" t="inlineStr">
+      <c r="N87" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N87" s="1" t="inlineStr">
+      <c r="O87" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O87" s="1" t="inlineStr">
+      <c r="P87" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P87" s="1" t="inlineStr">
+      <c r="Q87" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q87" s="1" t="inlineStr">
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R87" s="1" t="inlineStr">
+      <c r="S87" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S87" s="1" t="inlineStr">
+      <c r="T87" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T87" s="1" t="inlineStr">
+      <c r="U87" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U87" s="1" t="inlineStr">
+      <c r="V87" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V87" s="1" t="inlineStr">
+      <c r="W87" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W87" s="1" t="inlineStr">
+      <c r="X87" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X87" s="1" t="inlineStr">
+      <c r="Y87" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y87" s="1" t="inlineStr">
+      <c r="Z87" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z87" s="1" t="inlineStr">
+      <c r="AA87" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA87" s="1" t="inlineStr">
+      <c r="AB87" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB87" s="1" t="inlineStr">
+      <c r="AC87" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC87" s="1" t="inlineStr">
+      <c r="AD87" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7938,52 +8024,52 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Crawl Forward</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Crawl Forward</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>5127765a-3416-4ad4-82a8-b8fc1a631f9d</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>4beb2596-8710-4e51-b6df-d254dcd8295e</t>
         </is>
@@ -8000,52 +8086,52 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Crawl Backwards</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Crawl Backwards</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>b5603089-86cd-476f-9bde-990864a8807d</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>a5ee4830-2d8e-40c8-8e45-8b724ff15f5c</t>
         </is>
@@ -8062,92 +8148,92 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Hunting Claw</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Hunting Claw</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>fc3e40cc-71ec-4dfa-ae80-0b9d699a3d7d</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>ef78a0e7-25e4-4560-8efa-171d8c66d9ad</t>
         </is>
@@ -8164,92 +8250,92 @@
           <t>1 ,2</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Hunting Claw - Bear Scratch</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Hunting Claw - Bear Scratch</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>-10 -18</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>-10 -18</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>-1 +7</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>-1 +7</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>-1 +7</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>-1 +7</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>a1f1ccd7-98bb-49e0-98b4-e1d73528391d</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>9a7d4761-73a6-4220-8f1c-bc3c39c1e4d4</t>
         </is>
@@ -8266,92 +8352,92 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Bear Scratch</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Bear Scratch</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>f7e0a159-6c1e-47aa-a6b2-1d5086a8a90b</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>5860096e-aee1-4ee9-978e-45d8a1f9a66b</t>
         </is>
@@ -8368,97 +8454,97 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Grizzly Fling</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Grizzly Fling</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>e838ed18-0306-4d28-a55a-93c83adcfd53</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>e81234a3-67ae-4ebd-a575-d83d2d313e45</t>
         </is>
@@ -8475,57 +8561,57 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Mauling Bear</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Mauling Bear</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>Throw</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>Throw</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>0461098a-bfb9-4b4a-94ba-97614ce98201</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>8496a995-5956-4602-89b8-b58f679ea715</t>
         </is>
@@ -8542,87 +8628,87 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Bear Tackle</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Bear Tackle</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>5837afef-b8d2-4d46-a06a-8a12676a6390</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>05c7e692-8f53-4ed8-a91e-6a82ff495054</t>
         </is>
@@ -8659,125 +8745,130 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="H98" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H98" s="1" t="inlineStr">
+      <c r="I98" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I98" s="1" t="inlineStr">
+      <c r="J98" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J98" s="1" t="inlineStr">
+      <c r="K98" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="M98" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
+      <c r="P98" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q98" s="1" t="inlineStr">
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
+      <c r="S98" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S98" s="1" t="inlineStr">
+      <c r="T98" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T98" s="1" t="inlineStr">
+      <c r="U98" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U98" s="1" t="inlineStr">
+      <c r="V98" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V98" s="1" t="inlineStr">
+      <c r="W98" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W98" s="1" t="inlineStr">
+      <c r="X98" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X98" s="1" t="inlineStr">
+      <c r="Y98" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y98" s="1" t="inlineStr">
+      <c r="Z98" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z98" s="1" t="inlineStr">
+      <c r="AA98" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA98" s="1" t="inlineStr">
+      <c r="AB98" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB98" s="1" t="inlineStr">
+      <c r="AC98" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC98" s="1" t="inlineStr">
+      <c r="AD98" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8794,77 +8885,77 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Deadly Claw</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Deadly Claw</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>e184ee26-a99d-4a6e-a611-796573f789e4</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>bb1c29e3-58bb-45c9-8e71-2a10bba4cefc</t>
         </is>
@@ -8881,72 +8972,72 @@
           <t>b+1+2,f,df,d,db,b,ub,u,UF</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>– Rolling Bear</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Deadly Claw – Rolling Bear</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>35,40</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>!m</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>Rolling Bear is blockable.</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>e0d8a61c-bd7e-470f-9276-2019445b1af6</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>c0b6e513-8c5c-4215-b6c2-76d250cb8293</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
+      <c r="AC100" t="inlineStr">
         <is>
           <t>e184ee26-a99d-4a6e-a611-796573f789e4</t>
         </is>
@@ -8963,72 +9054,72 @@
           <t>b+1+2 ,3+4</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>– Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Deadly Claw – Hunting Bear Stance</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>HBS</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="R101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>35,-</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="T101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>!-</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
+      <c r="AA101" t="inlineStr">
         <is>
           <t>3080d799-3471-409f-a001-8460ec34ccbf</t>
         </is>
       </c>
-      <c r="AA101" t="inlineStr">
+      <c r="AB101" t="inlineStr">
         <is>
           <t>2d16e2c3-36ee-4f17-99b0-7c9b4ce32135</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
+      <c r="AC101" t="inlineStr">
         <is>
           <t>e184ee26-a99d-4a6e-a611-796573f789e4</t>
         </is>
@@ -9045,77 +9136,77 @@
           <t>b,b+2+3+4</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Fatal Wind</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Fatal Wind</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
+      <c r="R102" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="T102" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>593b9164-fa59-42cd-889a-96d606fcb5d2</t>
         </is>
       </c>
-      <c r="AA102" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>cd8f9f20-f853-4b67-9407-7c9691c689f1</t>
         </is>
@@ -9152,125 +9243,130 @@
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F105" s="1" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
+      <c r="H105" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H105" s="1" t="inlineStr">
+      <c r="I105" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I105" s="1" t="inlineStr">
+      <c r="J105" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J105" s="1" t="inlineStr">
+      <c r="K105" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K105" s="1" t="inlineStr">
+      <c r="L105" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L105" s="1" t="inlineStr">
+      <c r="M105" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M105" s="1" t="inlineStr">
+      <c r="N105" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N105" s="1" t="inlineStr">
+      <c r="O105" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O105" s="1" t="inlineStr">
+      <c r="P105" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P105" s="1" t="inlineStr">
+      <c r="Q105" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q105" s="1" t="inlineStr">
+      <c r="R105" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R105" s="1" t="inlineStr">
+      <c r="S105" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S105" s="1" t="inlineStr">
+      <c r="T105" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T105" s="1" t="inlineStr">
+      <c r="U105" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U105" s="1" t="inlineStr">
+      <c r="V105" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V105" s="1" t="inlineStr">
+      <c r="W105" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W105" s="1" t="inlineStr">
+      <c r="X105" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X105" s="1" t="inlineStr">
+      <c r="Y105" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y105" s="1" t="inlineStr">
+      <c r="Z105" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z105" s="1" t="inlineStr">
+      <c r="AA105" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA105" s="1" t="inlineStr">
+      <c r="AB105" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB105" s="1" t="inlineStr">
+      <c r="AC105" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC105" s="1" t="inlineStr">
+      <c r="AD105" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
